--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>103365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477140.9118680612</v>
+        <v>477141</v>
       </c>
       <c r="R2" t="n">
-        <v>6262416.796633986</v>
+        <v>6262417</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105744</v>
+        <v>105753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105753</v>
+        <v>105758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105758</v>
+        <v>105786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105786</v>
+        <v>105792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105792</v>
+        <v>105799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105799</v>
+        <v>105803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105803</v>
+        <v>105810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105813</v>
+        <v>105818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105818</v>
+        <v>105826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33730-2025 artfynd.xlsx
+++ b/artfynd/A 33730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74434426</v>
       </c>
       <c r="B2" t="n">
-        <v>105826</v>
+        <v>105836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
